--- a/diseases/d128/2015-2019.xlsx
+++ b/diseases/d128/2015-2019.xlsx
@@ -1209,9 +1209,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1605,9 +1602,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -2641,9 +2635,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -3677,9 +3668,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -4713,9 +4701,6 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -5897,9 +5882,6 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
@@ -6933,9 +6915,6 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
@@ -7969,9 +7948,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -9153,9 +9129,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -10189,9 +10162,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -11225,9 +11195,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -12409,9 +12376,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
@@ -13445,9 +13409,6 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
@@ -14629,9 +14590,6 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
@@ -15173,9 +15131,6 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -16209,9 +16164,6 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
@@ -17245,9 +17197,6 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
@@ -18429,9 +18378,6 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -19465,9 +19411,6 @@
       <c r="O127" t="n">
         <v>0</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0</v>
       </c>
@@ -20501,9 +20444,6 @@
       <c r="O134" t="n">
         <v>0</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0</v>
       </c>
@@ -21685,9 +21625,6 @@
       <c r="O142" t="n">
         <v>0</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0</v>
       </c>
@@ -22721,9 +22658,6 @@
       <c r="O149" t="n">
         <v>0</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0</v>
       </c>
@@ -23757,9 +23691,6 @@
       <c r="O156" t="n">
         <v>0</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0</v>
       </c>
@@ -24941,9 +24872,6 @@
       <c r="O164" t="n">
         <v>0</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0</v>
       </c>
@@ -25977,9 +25905,6 @@
       <c r="O171" t="n">
         <v>0</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0</v>
       </c>
@@ -27013,9 +26938,6 @@
       <c r="O178" t="n">
         <v>0</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0</v>
       </c>
@@ -28345,9 +28267,6 @@
       <c r="O187" t="n">
         <v>0</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>0</v>
       </c>
@@ -28741,9 +28660,6 @@
       <c r="O189" t="n">
         <v>0</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0</v>
       </c>
@@ -29777,9 +29693,6 @@
       <c r="O196" t="n">
         <v>0</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0</v>
       </c>
@@ -30813,9 +30726,6 @@
       <c r="O203" t="n">
         <v>0</v>
       </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
       <c r="R203" t="n">
         <v>0</v>
       </c>
@@ -31997,9 +31907,6 @@
       <c r="O211" t="n">
         <v>0</v>
       </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
       <c r="R211" t="n">
         <v>0</v>
       </c>
@@ -33033,9 +32940,6 @@
       <c r="O218" t="n">
         <v>0</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0</v>
       </c>
@@ -34069,9 +33973,6 @@
       <c r="O225" t="n">
         <v>0</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>0</v>
       </c>
@@ -35253,9 +35154,6 @@
       <c r="O233" t="n">
         <v>0</v>
       </c>
-      <c r="Q233" t="n">
-        <v>0</v>
-      </c>
       <c r="R233" t="n">
         <v>0</v>
       </c>
@@ -36289,9 +36187,6 @@
       <c r="O240" t="n">
         <v>0</v>
       </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
       <c r="R240" t="n">
         <v>0</v>
       </c>
@@ -37473,9 +37368,6 @@
       <c r="O248" t="n">
         <v>0</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>0</v>
       </c>
@@ -38509,9 +38401,6 @@
       <c r="O255" t="n">
         <v>0</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="R255" t="n">
         <v>0</v>
       </c>
@@ -39545,9 +39434,6 @@
       <c r="O262" t="n">
         <v>0</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="R262" t="n">
         <v>0</v>
       </c>
@@ -40729,9 +40615,6 @@
       <c r="O270" t="n">
         <v>0</v>
       </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
       <c r="R270" t="n">
         <v>0</v>
       </c>
@@ -41913,9 +41796,6 @@
       <c r="O278" t="n">
         <v>0</v>
       </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
       <c r="R278" t="n">
         <v>0</v>
       </c>
@@ -42309,9 +42189,6 @@
       <c r="O280" t="n">
         <v>0</v>
       </c>
-      <c r="Q280" t="n">
-        <v>0</v>
-      </c>
       <c r="R280" t="n">
         <v>0</v>
       </c>
@@ -43345,9 +43222,6 @@
       <c r="O287" t="n">
         <v>0</v>
       </c>
-      <c r="Q287" t="n">
-        <v>0</v>
-      </c>
       <c r="R287" t="n">
         <v>0</v>
       </c>
@@ -44381,9 +44255,6 @@
       <c r="O294" t="n">
         <v>0</v>
       </c>
-      <c r="Q294" t="n">
-        <v>0</v>
-      </c>
       <c r="R294" t="n">
         <v>0</v>
       </c>
@@ -45565,9 +45436,6 @@
       <c r="O302" t="n">
         <v>0</v>
       </c>
-      <c r="Q302" t="n">
-        <v>0</v>
-      </c>
       <c r="R302" t="n">
         <v>0</v>
       </c>
@@ -46601,9 +46469,6 @@
       <c r="O309" t="n">
         <v>0</v>
       </c>
-      <c r="Q309" t="n">
-        <v>0</v>
-      </c>
       <c r="R309" t="n">
         <v>0</v>
       </c>
@@ -47785,9 +47650,6 @@
       <c r="O317" t="n">
         <v>0</v>
       </c>
-      <c r="Q317" t="n">
-        <v>0</v>
-      </c>
       <c r="R317" t="n">
         <v>0</v>
       </c>
@@ -48821,9 +48683,6 @@
       <c r="O324" t="n">
         <v>0</v>
       </c>
-      <c r="Q324" t="n">
-        <v>0</v>
-      </c>
       <c r="R324" t="n">
         <v>0</v>
       </c>
@@ -49857,9 +49716,6 @@
       <c r="O331" t="n">
         <v>0</v>
       </c>
-      <c r="Q331" t="n">
-        <v>0</v>
-      </c>
       <c r="R331" t="n">
         <v>0</v>
       </c>
@@ -51041,9 +50897,6 @@
       <c r="O339" t="n">
         <v>0</v>
       </c>
-      <c r="Q339" t="n">
-        <v>0</v>
-      </c>
       <c r="R339" t="n">
         <v>0</v>
       </c>
@@ -52077,9 +51930,6 @@
       <c r="O346" t="n">
         <v>0</v>
       </c>
-      <c r="Q346" t="n">
-        <v>0</v>
-      </c>
       <c r="R346" t="n">
         <v>0</v>
       </c>
@@ -53113,9 +52963,6 @@
       <c r="O353" t="n">
         <v>0</v>
       </c>
-      <c r="Q353" t="n">
-        <v>0</v>
-      </c>
       <c r="R353" t="n">
         <v>0</v>
       </c>
@@ -54297,9 +54144,6 @@
       <c r="O361" t="n">
         <v>0</v>
       </c>
-      <c r="Q361" t="n">
-        <v>0</v>
-      </c>
       <c r="R361" t="n">
         <v>0</v>
       </c>
@@ -55481,9 +55325,6 @@
       <c r="O369" t="n">
         <v>0</v>
       </c>
-      <c r="Q369" t="n">
-        <v>0</v>
-      </c>
       <c r="R369" t="n">
         <v>0</v>
       </c>
@@ -55877,9 +55718,6 @@
       <c r="O371" t="n">
         <v>0</v>
       </c>
-      <c r="Q371" t="n">
-        <v>0</v>
-      </c>
       <c r="R371" t="n">
         <v>0</v>
       </c>
@@ -57061,9 +56899,6 @@
       <c r="O379" t="n">
         <v>0</v>
       </c>
-      <c r="Q379" t="n">
-        <v>0</v>
-      </c>
       <c r="R379" t="n">
         <v>0</v>
       </c>
@@ -58245,9 +58080,6 @@
       <c r="O387" t="n">
         <v>0</v>
       </c>
-      <c r="Q387" t="n">
-        <v>0</v>
-      </c>
       <c r="R387" t="n">
         <v>0</v>
       </c>
@@ -59281,9 +59113,6 @@
       <c r="O394" t="n">
         <v>0</v>
       </c>
-      <c r="Q394" t="n">
-        <v>0</v>
-      </c>
       <c r="R394" t="n">
         <v>0</v>
       </c>
@@ -60317,9 +60146,6 @@
       <c r="O401" t="n">
         <v>0</v>
       </c>
-      <c r="Q401" t="n">
-        <v>0</v>
-      </c>
       <c r="R401" t="n">
         <v>0</v>
       </c>
@@ -61501,9 +61327,6 @@
       <c r="O409" t="n">
         <v>0</v>
       </c>
-      <c r="Q409" t="n">
-        <v>0</v>
-      </c>
       <c r="R409" t="n">
         <v>0</v>
       </c>
@@ -62537,9 +62360,6 @@
       <c r="O416" t="n">
         <v>0</v>
       </c>
-      <c r="Q416" t="n">
-        <v>0</v>
-      </c>
       <c r="R416" t="n">
         <v>0</v>
       </c>
@@ -63573,9 +63393,6 @@
       <c r="O423" t="n">
         <v>0</v>
       </c>
-      <c r="Q423" t="n">
-        <v>0</v>
-      </c>
       <c r="R423" t="n">
         <v>0</v>
       </c>
@@ -65497,9 +65314,6 @@
       <c r="O436" t="n">
         <v>0</v>
       </c>
-      <c r="Q436" t="n">
-        <v>0</v>
-      </c>
       <c r="R436" t="n">
         <v>0</v>
       </c>
@@ -67125,9 +66939,6 @@
       <c r="O447" t="n">
         <v>0</v>
       </c>
-      <c r="Q447" t="n">
-        <v>0</v>
-      </c>
       <c r="R447" t="n">
         <v>0</v>
       </c>
@@ -68753,9 +68564,6 @@
       <c r="O458" t="n">
         <v>0</v>
       </c>
-      <c r="Q458" t="n">
-        <v>0</v>
-      </c>
       <c r="R458" t="n">
         <v>0</v>
       </c>
@@ -69787,9 +69595,6 @@
         <v>0</v>
       </c>
       <c r="O465" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q465" t="n">
         <v>0</v>
       </c>
       <c r="R465" t="n">
